--- a/data/delivery_zones.xlsx
+++ b/data/delivery_zones.xlsx
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Mannheim (Kafertal)</t>
+          <t>Mannheim (Käfertal)</t>
         </is>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Mannheim (Kafertal)</t>
+          <t>Mannheim (Käfertal)</t>
         </is>
       </c>
       <c r="C24" s="10" t="n"/>
